--- a/docs/descargas/tasa_fallecidos_100k.xlsx
+++ b/docs/descargas/tasa_fallecidos_100k.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" r:id="R0c707ef20c554b2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología" sheetId="2" r:id="Reace5c8d06a343b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2020" sheetId="3" r:id="Rfc7b42b03c8348ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2021" sheetId="4" r:id="R3e27b555fd9a435f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2022" sheetId="5" r:id="R442d11f48863467d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2023" sheetId="6" r:id="Rac2bef39807c4a29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2024" sheetId="7" r:id="Rc29f1a8ce5c94f2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" r:id="Rd2bbe26cabaa4ec8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología" sheetId="2" r:id="R82f54570cb7c4608"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2020" sheetId="3" r:id="Rd969b27df6124032"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2021" sheetId="4" r:id="Rf751e531028c4d5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2022" sheetId="5" r:id="R8b86088d1d514e97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2023" sheetId="6" r:id="R5e31a85fc0634f74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2024" sheetId="7" r:id="Rf48de0ef843b4143"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -561,7 +561,7 @@
         <x:v>Producto</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>Descarga pública del Catálogo de datos del Observatorio REDSA</x:v>
+        <x:v>Descarga pública del Catálogo de datos del Observatorio de Seguridad Vial y Movilidad Sostenible</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
